--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AC1467-91E3-4745-9553-4D537A6D652C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320A07E4-62FB-4F10-8E18-BC623B8593BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="217">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -55,15 +55,9 @@
     <t>attribute</t>
   </si>
   <si>
-    <t>category</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
-    <t>qualitative</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -373,9 +367,6 @@
     <t>identifier</t>
   </si>
   <si>
-    <t>quantitative</t>
-  </si>
-  <si>
     <t>numeric</t>
   </si>
   <si>
@@ -388,12 +379,6 @@
     <t>deprecated_names</t>
   </si>
   <si>
-    <t>atol_ontology_sample_type_milk</t>
-  </si>
-  <si>
-    <t>atol_ontology_sample_type_meat</t>
-  </si>
-  <si>
     <t>level_xx</t>
   </si>
   <si>
@@ -403,20 +388,6 @@
     <t>any other deprecated names separated by a comma and space [, ]</t>
   </si>
   <si>
-    <t>number in the ATOL ontology when the sample type is milk
-In some cases the synonym depends on the sample type. E.g. in lanupro_ontology a generic name is used for e.g. fatty acids independent of the sample type, while ATOL uses separate numbers for milk or meat.</t>
-  </si>
-  <si>
-    <t>number in the ATOL ontology when the sample type is meat
-In some cases the synonym depends on the sample type. E.g. in lanupro_ontology a generic name is used for e.g. fatty acids independent of the sample type, while ATOL uses separate numbers for milk or meat.</t>
-  </si>
-  <si>
-    <t>data category</t>
-  </si>
-  <si>
-    <t>dtring or numeric</t>
-  </si>
-  <si>
     <t>default variable unit when no units are specified in the variable name</t>
   </si>
   <si>
@@ -546,9 +517,6 @@
     <t>trt_rep_mg</t>
   </si>
   <si>
-    <t>nylon_pore_size_µm</t>
-  </si>
-  <si>
     <t>bag_size_cm2</t>
   </si>
   <si>
@@ -718,6 +686,15 @@
   </si>
   <si>
     <t>treatment replacement type (treatment which replaces a certain amount of substrate)</t>
+  </si>
+  <si>
+    <t>Format of the variable</t>
+  </si>
+  <si>
+    <t>nylon_pore_size_um</t>
+  </si>
+  <si>
+    <t>micro_meter</t>
   </si>
 </sst>
 </file>
@@ -2142,11 +2119,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E6D1A6-5A59-47F4-8744-F0D71D58BB8F}">
-  <dimension ref="A1:BP106"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="26.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2154,1199 +2166,1311 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M1" t="s">
+        <v>215</v>
+      </c>
+      <c r="N1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O1" t="s">
+        <v>158</v>
+      </c>
+      <c r="P1" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>205</v>
+      </c>
+      <c r="R1" t="s">
+        <v>163</v>
+      </c>
+      <c r="S1" t="s">
+        <v>126</v>
+      </c>
+      <c r="T1" t="s">
+        <v>209</v>
+      </c>
+      <c r="U1" t="s">
+        <v>152</v>
+      </c>
+      <c r="V1" t="s">
         <v>127</v>
       </c>
-      <c r="D1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H1" t="s">
-        <v>205</v>
-      </c>
-      <c r="I1" t="s">
-        <v>206</v>
-      </c>
-      <c r="J1" t="s">
-        <v>222</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="W1" t="s">
+        <v>210</v>
+      </c>
+      <c r="X1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB1" t="s">
         <v>164</v>
       </c>
-      <c r="L1" t="s">
+      <c r="AC1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AD1" t="s">
         <v>165</v>
       </c>
-      <c r="M1" t="s">
+      <c r="AE1" t="s">
         <v>166</v>
       </c>
-      <c r="N1" t="s">
+      <c r="AF1" t="s">
         <v>167</v>
       </c>
-      <c r="O1" t="s">
+      <c r="AG1" t="s">
         <v>168</v>
       </c>
-      <c r="P1" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R1" t="s">
-        <v>173</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="AH1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AK1" t="s">
         <v>135</v>
       </c>
-      <c r="T1" t="s">
-        <v>219</v>
-      </c>
-      <c r="U1" t="s">
-        <v>161</v>
-      </c>
-      <c r="V1" t="s">
-        <v>136</v>
-      </c>
-      <c r="W1" t="s">
-        <v>220</v>
-      </c>
-      <c r="X1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="AL1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ1" t="s">
         <v>142</v>
       </c>
-      <c r="Z1" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB1" t="s">
+      <c r="AR1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AS1" t="s">
         <v>174</v>
       </c>
-      <c r="AC1" t="s">
-        <v>204</v>
-      </c>
-      <c r="AD1" t="s">
+      <c r="AT1" t="s">
         <v>175</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AU1" t="s">
         <v>176</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AV1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AW1" t="s">
         <v>177</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AX1" t="s">
         <v>178</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AY1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>180</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>181</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>182</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>144</v>
+      </c>
+      <c r="BE1" t="s">
         <v>145</v>
       </c>
-      <c r="AI1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AJ1" t="s">
+      <c r="BF1" t="s">
         <v>146</v>
       </c>
-      <c r="AK1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AN1" t="s">
+      <c r="BG1" t="s">
         <v>147</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="BH1" t="s">
         <v>148</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="BI1" t="s">
+        <v>149</v>
+      </c>
+      <c r="BJ1" t="s">
         <v>150</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="BK1" t="s">
         <v>151</v>
       </c>
-      <c r="AR1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AS1" t="s">
+      <c r="BL1" t="s">
+        <v>140</v>
+      </c>
+      <c r="BM1" t="s">
         <v>184</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BN1" t="s">
         <v>185</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="BO1" t="s">
         <v>186</v>
       </c>
-      <c r="AV1" t="s">
-        <v>202</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>187</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>188</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>190</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>191</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>192</v>
-      </c>
-      <c r="BC1" t="s">
+      <c r="BP1" t="s">
         <v>193</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>153</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>155</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>156</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>157</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>158</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>159</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>160</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>149</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>194</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>195</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>196</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:68">
       <c r="A2" s="1" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="I2" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="J2" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="K2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="M2" t="s">
-        <v>112</v>
+        <v>107</v>
+      </c>
+      <c r="N2" t="s">
+        <v>107</v>
+      </c>
+      <c r="O2" t="s">
+        <v>5</v>
       </c>
       <c r="P2" t="s">
-        <v>112</v>
+        <v>5</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R2" t="s">
+        <v>107</v>
       </c>
       <c r="S2" t="s">
-        <v>112</v>
+        <v>5</v>
+      </c>
+      <c r="T2" t="s">
+        <v>106</v>
+      </c>
+      <c r="U2" t="s">
+        <v>107</v>
       </c>
       <c r="V2" t="s">
-        <v>112</v>
+        <v>5</v>
+      </c>
+      <c r="W2" t="s">
+        <v>106</v>
+      </c>
+      <c r="X2" t="s">
+        <v>107</v>
       </c>
       <c r="Y2" t="s">
-        <v>112</v>
+        <v>5</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:68">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
         <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>109</v>
       </c>
       <c r="F3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G3" t="s">
         <v>109</v>
       </c>
       <c r="H3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I3" t="s">
-        <v>207</v>
+        <v>109</v>
+      </c>
+      <c r="J3" t="s">
+        <v>109</v>
       </c>
       <c r="K3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L3" t="s">
         <v>109</v>
       </c>
+      <c r="M3" t="s">
+        <v>109</v>
+      </c>
       <c r="P3" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="S3" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="V3" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="Y3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:68">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>6</v>
-      </c>
-      <c r="P4" t="s">
-        <v>6</v>
-      </c>
-      <c r="S4" t="s">
-        <v>6</v>
-      </c>
-      <c r="V4" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:68" ht="158.4">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68" ht="158.4">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3"/>
-      <c r="AH5" s="3"/>
-      <c r="AI5" s="3"/>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
-      <c r="AO5" s="3"/>
-      <c r="AP5" s="3"/>
-      <c r="AQ5" s="3"/>
-      <c r="AR5" s="3"/>
-      <c r="AS5" s="3"/>
-      <c r="AT5" s="3"/>
-      <c r="AU5" s="3"/>
-      <c r="AV5" s="3"/>
-      <c r="AW5" s="3"/>
-      <c r="AX5" s="3"/>
-      <c r="AY5" s="3"/>
-      <c r="AZ5" s="3"/>
-      <c r="BA5" s="3"/>
-      <c r="BB5" s="3"/>
-      <c r="BC5" s="3"/>
-      <c r="BD5" s="3"/>
-      <c r="BE5" s="3"/>
-      <c r="BF5" s="3"/>
-      <c r="BG5" s="3"/>
-      <c r="BH5" s="3"/>
-      <c r="BI5" s="3"/>
-      <c r="BJ5" s="3"/>
-      <c r="BK5" s="3"/>
-      <c r="BL5" s="3"/>
-      <c r="BM5" s="3"/>
-      <c r="BN5" s="3"/>
-      <c r="BO5" s="3"/>
-      <c r="BP5" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+      <c r="AO4" s="3"/>
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3"/>
+      <c r="AU4" s="3"/>
+      <c r="AV4" s="3"/>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+      <c r="AZ4" s="3"/>
+      <c r="BA4" s="3"/>
+      <c r="BB4" s="3"/>
+      <c r="BC4" s="3"/>
+      <c r="BD4" s="3"/>
+      <c r="BE4" s="3"/>
+      <c r="BF4" s="3"/>
+      <c r="BG4" s="3"/>
+      <c r="BH4" s="3"/>
+      <c r="BI4" s="3"/>
+      <c r="BJ4" s="3"/>
+      <c r="BK4" s="3"/>
+      <c r="BL4" s="3"/>
+      <c r="BM4" s="3"/>
+      <c r="BN4" s="3"/>
+      <c r="BO4" s="3"/>
+      <c r="BP4" s="3"/>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L5" t="s">
+        <v>119</v>
+      </c>
+      <c r="M5" t="s">
+        <v>216</v>
+      </c>
+      <c r="P5" t="s">
+        <v>109</v>
+      </c>
+      <c r="S5" t="s">
+        <v>109</v>
+      </c>
+      <c r="V5" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="6" spans="1:68">
       <c r="A6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" t="s">
-        <v>128</v>
-      </c>
-      <c r="F6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" t="s">
-        <v>128</v>
-      </c>
-      <c r="L6" t="s">
-        <v>128</v>
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" t="s">
+        <v>188</v>
+      </c>
+      <c r="O6" t="s">
+        <v>159</v>
       </c>
       <c r="P6" t="s">
-        <v>112</v>
+        <v>129</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>188</v>
       </c>
       <c r="S6" t="s">
-        <v>112</v>
+        <v>129</v>
+      </c>
+      <c r="T6" t="s">
+        <v>188</v>
       </c>
       <c r="V6" t="s">
-        <v>112</v>
+        <v>129</v>
+      </c>
+      <c r="W6" t="s">
+        <v>188</v>
       </c>
       <c r="Y6" t="s">
-        <v>112</v>
+        <v>129</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:68">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J7" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="K7" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="O7" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q7" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="S7" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="T7" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="V7" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="W7" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Y7" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Z7" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:68">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K8" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="O8" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="Q8" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="S8" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="T8" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="V8" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="W8" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="Y8" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="Z8" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:68">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="K9" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="O9" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="P9" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="Q9" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="S9" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="T9" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="V9" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="W9" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="Y9" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="Z9" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:68">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>169</v>
-      </c>
-      <c r="K10" t="s">
-        <v>213</v>
-      </c>
-      <c r="O10" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="P10" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="S10" t="s">
-        <v>169</v>
-      </c>
-      <c r="T10" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="V10" t="s">
-        <v>169</v>
-      </c>
-      <c r="W10" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="Y10" t="s">
-        <v>169</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:68">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="P11" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="S11" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="V11" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="Y11" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:68">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="P12" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="S12" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="V12" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="Y12" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:68">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="S13" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="V13" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="Y13" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:68">
       <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" t="s">
-        <v>218</v>
-      </c>
-      <c r="P14" t="s">
-        <v>218</v>
-      </c>
-      <c r="S14" t="s">
-        <v>218</v>
-      </c>
-      <c r="V14" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>218</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:68">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:68">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E7C548E2-2325-4A89-AACC-A6B62EAB9082}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F9775362-37DE-4C42-A53C-5729AB9A9A59}">
           <x14:formula1>
-            <xm:f>description!$E$6:$I$6</xm:f>
+            <xm:f>description!$D$3:$H$3</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:BP3</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2FF45D2A-73AF-47B4-9EFA-3A4BFC648610}">
-          <x14:formula1>
-            <xm:f>description!$E$7:$H$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B4:BP4</xm:sqref>
+          <xm:sqref>B2:XFD2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3356,189 +3480,119 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68D4BA7-81A7-496D-83F7-4CE2A3B40B1B}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+      <c r="G3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="57.6">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="57.6">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>109</v>
-      </c>
-      <c r="I6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>141</v>
+      <c r="C7" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62FCB55D-2760-428F-B00C-77E87AFC19C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985BBC10-AEF2-4D9E-8D0D-CC81BF46781E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
   <sheets>
-    <sheet name="lanupro_vocabulary_incubations" sheetId="1" r:id="rId1"/>
+    <sheet name="vocabulary" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
     <definedName name="Analyst">#REF!:INDEX(#REF!,COUNTA(#REF!))</definedName>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">lanupro_vocabulary_incubations!$A:$BU</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">vocabulary!$A:$BU</definedName>
     <definedName name="factor_dropdown">IF(_xlfn.XLOOKUP([1]scientific_sheet!A$1,[1]!lanupro_vocabulary_combined[#Headers],INDEX([1]!lanupro_vocabulary_combined[#Data],MATCH("type",[1]!lanupro_vocabulary_combined[lanupro_ontology],0),0))="factor",INDIRECT("lanupro_vocabulary_combined["&amp;[1]scientific_sheet!A$1&amp;"]"),"")</definedName>
     <definedName name="GC">#REF!:INDEX(#REF!,COUNTA(#REF!))</definedName>
     <definedName name="GC_method">#REF!:INDEX(#REF!,COUNTA(#REF!))</definedName>

--- a/data/raw_results/lanupro_vocabulary_incubations.xlsx
+++ b/data/raw_results/lanupro_vocabulary_incubations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985BBC10-AEF2-4D9E-8D0D-CC81BF46781E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED452D8-BA4F-4133-97A8-03C390A565EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{7197A02B-EEB4-4DD3-A670-5499E50D1EFE}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7956" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7956" uniqueCount="239">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -780,6 +780,30 @@
   </si>
   <si>
     <t>level_100</t>
+  </si>
+  <si>
+    <t>YS_substrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD_substrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HF_substrate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YS_inoculum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD_inoculum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HF_inoculum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4701,7 +4725,7 @@
         <v>84</v>
       </c>
       <c r="U14" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="V14" t="s">
         <v>84</v>
@@ -4710,7 +4734,7 @@
         <v>84</v>
       </c>
       <c r="X14" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="Y14" t="s">
         <v>84</v>
@@ -4719,7 +4743,7 @@
         <v>84</v>
       </c>
       <c r="AA14" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="AB14" t="s">
         <v>84</v>
@@ -4728,7 +4752,7 @@
         <v>84</v>
       </c>
       <c r="AD14" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="AE14" t="s">
         <v>84</v>
@@ -4931,7 +4955,7 @@
         <v>84</v>
       </c>
       <c r="U15" t="s">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="V15" t="s">
         <v>84</v>
@@ -4940,7 +4964,7 @@
         <v>84</v>
       </c>
       <c r="X15" t="s">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="Y15" t="s">
         <v>84</v>
@@ -4949,7 +4973,7 @@
         <v>84</v>
       </c>
       <c r="AA15" t="s">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="AB15" t="s">
         <v>84</v>
@@ -4958,7 +4982,7 @@
         <v>84</v>
       </c>
       <c r="AD15" t="s">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="AE15" t="s">
         <v>84</v>
@@ -5161,7 +5185,7 @@
         <v>84</v>
       </c>
       <c r="U16" t="s">
-        <v>84</v>
+        <v>235</v>
       </c>
       <c r="V16" t="s">
         <v>84</v>
@@ -5170,7 +5194,7 @@
         <v>84</v>
       </c>
       <c r="X16" t="s">
-        <v>84</v>
+        <v>235</v>
       </c>
       <c r="Y16" t="s">
         <v>84</v>
@@ -5179,7 +5203,7 @@
         <v>84</v>
       </c>
       <c r="AA16" t="s">
-        <v>84</v>
+        <v>235</v>
       </c>
       <c r="AB16" t="s">
         <v>84</v>
@@ -5188,7 +5212,7 @@
         <v>84</v>
       </c>
       <c r="AD16" t="s">
-        <v>84</v>
+        <v>235</v>
       </c>
       <c r="AE16" t="s">
         <v>84</v>
@@ -5391,7 +5415,7 @@
         <v>84</v>
       </c>
       <c r="U17" t="s">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="V17" t="s">
         <v>84</v>
@@ -5400,7 +5424,7 @@
         <v>84</v>
       </c>
       <c r="X17" t="s">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="Y17" t="s">
         <v>84</v>
@@ -5409,7 +5433,7 @@
         <v>84</v>
       </c>
       <c r="AA17" t="s">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="AB17" t="s">
         <v>84</v>
@@ -5418,7 +5442,7 @@
         <v>84</v>
       </c>
       <c r="AD17" t="s">
-        <v>84</v>
+        <v>236</v>
       </c>
       <c r="AE17" t="s">
         <v>84</v>
@@ -5621,7 +5645,7 @@
         <v>84</v>
       </c>
       <c r="U18" t="s">
-        <v>84</v>
+        <v>237</v>
       </c>
       <c r="V18" t="s">
         <v>84</v>
@@ -5630,7 +5654,7 @@
         <v>84</v>
       </c>
       <c r="X18" t="s">
-        <v>84</v>
+        <v>237</v>
       </c>
       <c r="Y18" t="s">
         <v>84</v>
@@ -5639,7 +5663,7 @@
         <v>84</v>
       </c>
       <c r="AA18" t="s">
-        <v>84</v>
+        <v>237</v>
       </c>
       <c r="AB18" t="s">
         <v>84</v>
@@ -5648,7 +5672,7 @@
         <v>84</v>
       </c>
       <c r="AD18" t="s">
-        <v>84</v>
+        <v>237</v>
       </c>
       <c r="AE18" t="s">
         <v>84</v>
@@ -5851,7 +5875,7 @@
         <v>84</v>
       </c>
       <c r="U19" t="s">
-        <v>84</v>
+        <v>238</v>
       </c>
       <c r="V19" t="s">
         <v>84</v>
@@ -5860,7 +5884,7 @@
         <v>84</v>
       </c>
       <c r="X19" t="s">
-        <v>84</v>
+        <v>238</v>
       </c>
       <c r="Y19" t="s">
         <v>84</v>
@@ -5869,7 +5893,7 @@
         <v>84</v>
       </c>
       <c r="AA19" t="s">
-        <v>84</v>
+        <v>238</v>
       </c>
       <c r="AB19" t="s">
         <v>84</v>
@@ -5878,7 +5902,7 @@
         <v>84</v>
       </c>
       <c r="AD19" t="s">
-        <v>84</v>
+        <v>238</v>
       </c>
       <c r="AE19" t="s">
         <v>84</v>
